--- a/Zerde_Sandar_qupiyasy/Zertteu_kestesi.xlsx
+++ b/Zerde_Sandar_qupiyasy/Zertteu_kestesi.xlsx
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -886,8 +886,16 @@
           <t>Қиял-ғажайып</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="7" t="n"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік [Мәтін] : қазақтың көне ертегілері (жаңартылған нұсқа) / М. Байбеков О. Байбеков ... – Тараз : Сенім, 2019</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="6" t="n"/>
     </row>
@@ -905,8 +913,16 @@
           <t>Қиял-ғажайып</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>https://adebiportal.kz/kz/balaqai/view/kerqula-atty-kendebai__126</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="6" t="n"/>
     </row>
@@ -924,8 +940,16 @@
           <t>Қиял-ғажайып</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа – Алматы, 1972.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="6" t="n"/>
     </row>
@@ -943,8 +967,16 @@
           <t>Қиял-ғажайып</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>https://bilim-all.kz/article/263</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
@@ -962,8 +994,16 @@
           <t>Қиял-ғажайып</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Қаңбақ шал [Text] : халық ертегісі / Сыздықов Жақан ... – Алма-Ата : Қазақстан көркем әдебиет баспасы, 1937</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="6" t="n"/>
     </row>
@@ -973,16 +1013,24 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Мақта қыз бен мысық</t>
+          <t>Тазшаның қырық өтірігі</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Хайуанаттар</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="7" t="n"/>
+          <t>Тұрмыс-салт</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>https://bilim-all.kz/article/2647</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="6" t="n"/>
     </row>
@@ -992,155 +1040,30 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Түлкі мен бөдене</t>
+          <t>Аяз би</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Хайуанаттар</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="7" t="n"/>
+          <t>Тұрмыс-салт</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>https://bilimdiler.kz/okushi/27654-ayaz-bi-ertegisi.html</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="6" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Жыл басына таласқан хайуанаттар</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Хайуанаттар</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Тазшаның қырық өтірігі</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Тұрмыс-салт</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Алдар Көсе әңгімелері</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Тұрмыс-салт</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Аяз би</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Тұрмыс-салт</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Жиренше шешен</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Тұрмыс-салт</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Бір атым насыбай</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Тұрмыс-салт</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Жеті қарақшы</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Аңыз-ертегі</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="6" t="n"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 F2 F3 F4 F5 F6 F7 F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"иә,жоқ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1304,1365 +1227,3018 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C2" s="4">
-        <f>IFERROR(VLOOKUP(B2,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B2,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>үш жан</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C3" s="4">
-        <f>IFERROR(VLOOKUP(B3,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B3,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>тоғыз қабат кетпен</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C4" s="4">
-        <f>IFERROR(VLOOKUP(B4,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B4,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Тоғызы жылқы</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C5" s="4">
-        <f>IFERROR(VLOOKUP(B5,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B5,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>тоғыз ұл</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C6" s="4">
-        <f>IFERROR(VLOOKUP(B6,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B6,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>тоғыз қара сандық</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C7" s="4">
-        <f>IFERROR(VLOOKUP(B7,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B7,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Темір ханның елі жеті айлық жер екен</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C8" s="4">
-        <f>IFERROR(VLOOKUP(B8,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B8,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>жеті аяқты жирен ат</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C9" s="4">
-        <f>IFERROR(VLOOKUP(B9,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B9,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>қырық күн тойы</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C10" s="4">
-        <f>IFERROR(VLOOKUP(B10,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B10,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>қырық құлаш үлкен қазаны</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C11" s="4">
-        <f>IFERROR(VLOOKUP(B11,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B11,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>қырық құлаш қайыс белбеуі</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C12" s="4">
-        <f>IFERROR(VLOOKUP(B12,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B12,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>қырық елік</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C13" s="4">
-        <f>IFERROR(VLOOKUP(B13,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B13,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>бір айда бір жастағы баладай</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C14" s="4">
-        <f>IFERROR(VLOOKUP(B14,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B14,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Сенің сегіз қызың бір төбе, Кенжекейің бір төбе болса, менің сегіз ұлым бір төбе, Төстігім бір төбе еді.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C15" s="4">
-        <f>IFERROR(VLOOKUP(B15,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B15,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>екі айда екі жастағы баладай</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C16" s="4">
-        <f>IFERROR(VLOOKUP(B16,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B16,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Самұрықтың екі басы</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C17" s="4">
-        <f>IFERROR(VLOOKUP(B17,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B17,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>алты аяқты ала ат</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C18" s="4">
-        <f>IFERROR(VLOOKUP(B18,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B18,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>алты таудың ар жағы</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C19" s="4">
-        <f>IFERROR(VLOOKUP(B19,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B19,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>жеті көлдің желкесіндегі</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C20" s="4">
-        <f>IFERROR(VLOOKUP(B20,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B20,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>алты айлық жол</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C21" s="4">
-        <f>IFERROR(VLOOKUP(B21,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B21,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>сегіз ұлы</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C22" s="4">
-        <f>IFERROR(VLOOKUP(B22,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B22,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Отыз күн ойын</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C23" s="4">
-        <f>IFERROR(VLOOKUP(B23,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B23,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>бір жылдық азық</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C24" s="4">
-        <f>IFERROR(VLOOKUP(B24,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B24,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>бір тал қыл</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C25" s="4">
-        <f>IFERROR(VLOOKUP(B25,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B25,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>бір алтын құйрықты, құндыз жүнді құлын</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C26" s="4">
-        <f>IFERROR(VLOOKUP(B26,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B26,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Тұман ашылғанда қыздың орнында екі бөлінген кемпір жатады.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C27" s="4">
-        <f>IFERROR(VLOOKUP(B27,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B27,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Бұл жолымызда үш бөгет бар.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C28" s="4">
-        <f>IFERROR(VLOOKUP(B28,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B28,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>алты сағатта алты айлық жол</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="n"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C29" s="4">
-        <f>IFERROR(VLOOKUP(B29,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B29,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>алты аққу Кендебайдың төбесінен алты айналып ұшып, жақындап келеді</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="n"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C30" s="4">
-        <f>IFERROR(VLOOKUP(B30,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B30,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>алты күн қатарынан ұйықтайтын</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="n"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C31" s="4">
-        <f>IFERROR(VLOOKUP(B31,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B31,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Алты айдың ішінде алты кез ат</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C32" s="4">
-        <f>IFERROR(VLOOKUP(B32,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B32,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>алты қырдың ар жағынан қаша жөнелген құлан</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C33" s="4">
-        <f>IFERROR(VLOOKUP(B33,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B33,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>алты күнде күліпті, алпыс күнде жүріпті, алты жылда жігіт болыпты.</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="n"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C34" s="4">
-        <f>IFERROR(VLOOKUP(B34,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B34,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>жеті басты дәу</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C35" s="4">
-        <f>IFERROR(VLOOKUP(B35,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B35,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Осылай ерсілі-қарсылы жеті өтіп, жеті рет соққанда жеті басы бірдей ұшып кетіп, дәу төңкеріле құлайды.</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="n"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C36" s="4">
-        <f>IFERROR(VLOOKUP(B36,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B36,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>алтын құйрықты сегіз құлын, құйрығы жоқ бір құлын алтын науадан су ішіп тұр екен.</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C37" s="4">
-        <f>IFERROR(VLOOKUP(B37,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B37,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Тоғыз ай, тоғыз күн болғанда, әйел толғатып, босаныпты.</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="n"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C38" s="4">
-        <f>IFERROR(VLOOKUP(B38,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B38,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>отыз күн ойын, қырық күн тойы</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C39" s="4">
-        <f>IFERROR(VLOOKUP(B39,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B39,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>отыз күн ойын, қырық күн тойы</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="n"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C40" s="4">
-        <f>IFERROR(VLOOKUP(B40,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B40,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>жүз батпан шоқпар</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="n"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C41" s="4">
-        <f>IFERROR(VLOOKUP(B41,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B41,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>бір қып-қызыл өкпе жүзіп жүр екен</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="n"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C42" s="4">
-        <f>IFERROR(VLOOKUP(B42,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B42,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>бір перзентке зар болыпты</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="n"/>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C43" s="4">
-        <f>IFERROR(VLOOKUP(B43,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B43,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>кемпір бір тісін жұлып алып, атып жібергенде, тайдың бір аяғын жұлып түсіреді.</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="n"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C44" s="4">
-        <f>IFERROR(VLOOKUP(B44,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B44,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>бір қызыл түлкі келеді де кемпірге:
+— Шеше, шаршаған екенсің, мен қаза тұрайын, сен ұйықтап демал, –дейді.</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="n"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C45" s="4">
-        <f>IFERROR(VLOOKUP(B45,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B45,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Тай екі аяғымен шауып бара жатып, жолында бір бәйтерекке кез болады.</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="n"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C46" s="4">
-        <f>IFERROR(VLOOKUP(B46,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B46,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Тай үш аяғымен қашып, жеткізбейді</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="n"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C47" s="4">
-        <f>IFERROR(VLOOKUP(B47,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B47,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Жайлаудағы бес төбетіме хабар айта кет, мені жалмауыз кемпірден арашалап алсын, – дейді.</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="n"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C48" s="4">
-        <f>IFERROR(VLOOKUP(B48,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B48,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Сол уақытта қырық ұры саған ет пісіртіп, қарап тұрар.</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="n"/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C49" s="4">
-        <f>IFERROR(VLOOKUP(B49,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B49,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Ертеңіне қырық қызды бір түсті киіндіріп, қатарлап қояды.</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="n"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C50" s="4">
-        <f>IFERROR(VLOOKUP(B50,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B50,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Ең алдымен хан, оның соңынан қырық уәзірі жүрсін, ең артында өзің жүр, – дейді.</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="n"/>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C51" s="4">
-        <f>IFERROR(VLOOKUP(B51,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B51,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>алтын мүйізді бір шұбар киік бар</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="n"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C52" s="4">
-        <f>IFERROR(VLOOKUP(B52,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B52,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Бірнеше күн жүріп келе жатса, алдынан екі алақанына екі тауды салып жүрген бір дәу кездеседі.</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="n"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C53" s="4">
-        <f>IFERROR(VLOOKUP(B53,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B53,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Тағы да жүріп келе жатса, алдынан екі көлдің суын екі ұртына ұрттап жүрген тағы бір дәу кез болады.</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="n"/>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C54" s="4">
-        <f>IFERROR(VLOOKUP(B54,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B54,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Келе жатса, екі аяғына екі батпан тас байлап алған, ойдан-қырдан жүгіріп жүрген желаяққа кез болады.</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="n"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C55" s="4">
-        <f>IFERROR(VLOOKUP(B55,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B55,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Екі күншілік жер қалды</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="n"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C56" s="4">
-        <f>IFERROR(VLOOKUP(B56,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B56,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Баланың жолдастарымен келе жатқанын ит жүз шақырымнан біліп алдарынан шығады.</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="n"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C57" s="4">
-        <f>IFERROR(VLOOKUP(B57,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B57,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Мың ділдә берсеңіз, істей аламын</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="n"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Қаңбақ шал</t>
+        </is>
+      </c>
       <c r="C58" s="4">
-        <f>IFERROR(VLOOKUP(B58,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B58,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Қараса, бір дәу екі тауды біріне-бірін шақпақ қылып, ұрып тұр екен</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="n"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Қаңбақ шал</t>
+        </is>
+      </c>
       <c r="C59" s="4">
-        <f>IFERROR(VLOOKUP(B59,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="7" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B59,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Үш дәу тым-тырақай қаша жөнеледі.</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="n"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Қаңбақ шал</t>
+        </is>
+      </c>
       <c r="C60" s="4">
-        <f>IFERROR(VLOOKUP(B60,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B60,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>бергі атаңда бес атамның құны бар,</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Қаңбақ шал</t>
+        </is>
+      </c>
       <c r="C61" s="4">
-        <f>IFERROR(VLOOKUP(B61,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B61,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Арғы атаңда алты атамның құны бар</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="n"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C62" s="4">
-        <f>IFERROR(VLOOKUP(B62,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B62,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Мен барып, Уәлібайдың қызына сырттан хабарласқанда, ол маған бір тәрелке, бір қайрақ, бір пышақ, бір гауһар тас беріп жіберді.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="n"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C63" s="4">
-        <f>IFERROR(VLOOKUP(B63,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D63" s="7" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B63,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Хан не дерін білмейді, бір қызарады, бір бозарады, жерге кіріп кеткендей болады, ақырында:</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="n"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C64" s="4">
-        <f>IFERROR(VLOOKUP(B64,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B64,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>«Адамзатқа пайдалы үш затым бар, біреуі - қыдыр, біреуі - бақыт, біреуі - ақыл, осының бірін ал»</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="6" t="n"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C65" s="4">
-        <f>IFERROR(VLOOKUP(B65,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="7" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B65,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Қырық уәзір үш күншілік жерге шығарып салып қайтады</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="6" t="n"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C66" s="4">
-        <f>IFERROR(VLOOKUP(B66,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B66,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>алты қанат ақ боз үй</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="6" t="n"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C67" s="4">
-        <f>IFERROR(VLOOKUP(B67,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B67,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Мен жеті атамнан бері ханмын</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="6" t="n"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C68" s="4">
-        <f>IFERROR(VLOOKUP(B68,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D68" s="7" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B68,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>сол жерде отыз тоғыз атты сойып, бір атты қалдырып, сойған аттардың біреуінің етін өздерінің киімін жағып пісіріп, етін жеп алады.</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="6" t="n"/>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C69" s="4">
-        <f>IFERROR(VLOOKUP(B69,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B69,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Он бір ай уақыт беремін.</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="n"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C70" s="4">
-        <f>IFERROR(VLOOKUP(B70,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B70,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>отыз күн ойын, қырық күн тойын</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="6" t="n"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C71" s="4">
-        <f>IFERROR(VLOOKUP(B71,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D71" s="7" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B71,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>отыз күн ойын, қырық күн тойын</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="6" t="n"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C72" s="4">
-        <f>IFERROR(VLOOKUP(B72,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D72" s="7" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B72,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Сиыр күніне қырық суарсаң да судан айдағанда, аузын суға малмай, артқы аяғын сілікпей, өтпеуші еді.</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="6" t="n"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C73" s="4">
-        <f>IFERROR(VLOOKUP(B73,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D73" s="7" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B73,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>менің қырық асыранды қазым бар,</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Н</t>
+        </is>
+      </c>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="6" t="n"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C74" s="4">
-        <f>IFERROR(VLOOKUP(B74,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D74" s="7" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B74,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Ханның «Қырық асыранды қазым бар, соны қан шығармай сойып, білдірмей жұлып, күйдірмей пісіріп беретін кісі бар ма?» дегені: «Менің ақылсыз қырық уәзірім бар, соларды ұрмай-соқпай жөнге салып беретін кісі бар ма?» дегені еді.</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Адам, кейіпкер</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="6" t="n"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Аяз би</t>
+        </is>
+      </c>
       <c r="C75" s="4">
-        <f>IFERROR(VLOOKUP(B75,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="7" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B75,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>«Дәудің інжулі қара арғымағы бар, бір шапқанда жүз шақырым шабады» дейді.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="6" t="n"/>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C76" s="4">
-        <f>IFERROR(VLOOKUP(B76,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B76,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Еншіге әкем берген мың қоянның
+Сол қыста қырып алдым барлық туын.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="6" t="n"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C77" s="4">
-        <f>IFERROR(VLOOKUP(B77,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="7" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B77,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Үш жаста мергеншілік кәсіп қылдым,
+Ши оқпен мың құланды атып қырдым.</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="6" t="n"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C78" s="4">
-        <f>IFERROR(VLOOKUP(B78,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="7" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B78,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Жүз салған қорғасыннан қара балтам,
+Шықпады он матадан сыңар қалтам.
+Дәулеттің маған келген арқасында,
+Көшкенде жүз түлкіге жүгімді артам.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="6" t="n"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C79" s="4">
-        <f>IFERROR(VLOOKUP(B79,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="7" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B79,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>қырық ауыз өтірікті өлең қылып айтса</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="6" t="n"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C80" s="4">
-        <f>IFERROR(VLOOKUP(B80,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="7" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B80,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Ізіне аттың басқан қақ тұрыпты,
+Қырық құлаш қармақ салып, жайын алдым.</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="6" t="n"/>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C81" s="4">
-        <f>IFERROR(VLOOKUP(B81,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="7" t="n"/>
-      <c r="E81" s="6" t="n"/>
-      <c r="F81" s="6" t="n"/>
-      <c r="G81" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B81,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Көлбақаның көлектей иегі бар,
+Көртышқанның қырық құлаш үйегі бар.
+Өзім барып, жерінен алып келдім,
+Бір түлкінің қырық арба сүйегі бар!</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="6" t="n"/>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C82" s="4">
-        <f>IFERROR(VLOOKUP(B82,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="7" t="n"/>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="6" t="n"/>
-      <c r="G82" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B82,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Еріген  майда ыдысқа қотарғанымда, бір түйе қарнына, бір өгіз қарнына, бір борсық қарнына әрең-әрең сыйды.</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Жануар</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="6" t="n"/>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C83" s="4">
-        <f>IFERROR(VLOOKUP(B83,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="7" t="n"/>
-      <c r="E83" s="6" t="n"/>
-      <c r="F83" s="6" t="n"/>
-      <c r="G83" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B83,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ұялғаннан екі беті қып-қызыл болып кетті</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="6" t="n"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C84" s="4">
-        <f>IFERROR(VLOOKUP(B84,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="7" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="6" t="n"/>
-      <c r="G84" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B84,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>үш күн, үш түнде барып есіме түсе қалды</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="6" t="n"/>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C85" s="4">
-        <f>IFERROR(VLOOKUP(B85,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="7" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B85,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Міндім де қара қоңыз сона қудым,
+Үш жұма, үш ай жүріп, қона қудым.</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Уақыт</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="6" t="n"/>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C86" s="4">
-        <f>IFERROR(VLOOKUP(B86,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B86,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Жонынан атжалманның айыл алдым,
+Үш жерге ішін жарып майын алдым.</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="6" t="n"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C87" s="4">
-        <f>IFERROR(VLOOKUP(B87,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="7" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B87,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Жүрегін құрқылтайдың төрт бөліп жеп,
+Нансаңыз, өмірімде бір-ақ тойдым.</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="6" t="n"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C88" s="4">
-        <f>IFERROR(VLOOKUP(B88,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="7" t="n"/>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B88,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Қақалып кеше кешке жеген етке.
+Қолқамда бес жыл тұрды кәрі жілік.</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Дене мүшесі</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="6" t="n"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C89" s="4">
-        <f>IFERROR(VLOOKUP(B89,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B89,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Алты құлаш ала биеден туған, жеті құлаш жирен құлыным жылқының ішінде де жоқ, ұры алғанын білмедім,</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="6" t="n"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C90" s="4">
-        <f>IFERROR(VLOOKUP(B90,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B90,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Алты құлаш ала биеден туған, жеті құлаш жирен құлыным жылқының ішінде де жоқ, ұры алғанын білмедім,</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Жер, қашықтық</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="6" t="n"/>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C91" s="4">
-        <f>IFERROR(VLOOKUP(B91,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="6" t="n"/>
-      <c r="F91" s="6" t="n"/>
-      <c r="G91" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B91,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Аспанға алты жерден тіреу қойдым.</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Зат, мүлік</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="6" t="n"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Тазшаның қырық өтірігі</t>
+        </is>
+      </c>
       <c r="C92" s="4">
-        <f>IFERROR(VLOOKUP(B92,Ертегілер!$B$2:$C$15,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="7" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="7" t="n"/>
+        <f>IFERROR(VLOOKUP(B92,Ертегілер!$B$2:$C$8,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Алты күндей ақ боран соғып еді,
+Жалғыз қурай ығында ас қып іштім.</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
@@ -2671,7 +4247,7 @@
       </c>
       <c r="B93" s="6" t="n"/>
       <c r="C93" s="4">
-        <f>IFERROR(VLOOKUP(B93,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B93,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D93" s="7" t="n"/>
@@ -2686,7 +4262,7 @@
       </c>
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="4">
-        <f>IFERROR(VLOOKUP(B94,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B94,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D94" s="7" t="n"/>
@@ -2701,7 +4277,7 @@
       </c>
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="4">
-        <f>IFERROR(VLOOKUP(B95,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B95,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D95" s="7" t="n"/>
@@ -2716,7 +4292,7 @@
       </c>
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="4">
-        <f>IFERROR(VLOOKUP(B96,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B96,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D96" s="7" t="n"/>
@@ -2731,7 +4307,7 @@
       </c>
       <c r="B97" s="6" t="n"/>
       <c r="C97" s="4">
-        <f>IFERROR(VLOOKUP(B97,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B97,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D97" s="7" t="n"/>
@@ -2746,7 +4322,7 @@
       </c>
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="4">
-        <f>IFERROR(VLOOKUP(B98,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B98,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D98" s="7" t="n"/>
@@ -2761,7 +4337,7 @@
       </c>
       <c r="B99" s="6" t="n"/>
       <c r="C99" s="4">
-        <f>IFERROR(VLOOKUP(B99,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B99,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D99" s="7" t="n"/>
@@ -2776,7 +4352,7 @@
       </c>
       <c r="B100" s="6" t="n"/>
       <c r="C100" s="4">
-        <f>IFERROR(VLOOKUP(B100,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B100,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D100" s="7" t="n"/>
@@ -2791,7 +4367,7 @@
       </c>
       <c r="B101" s="6" t="n"/>
       <c r="C101" s="4">
-        <f>IFERROR(VLOOKUP(B101,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B101,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D101" s="7" t="n"/>
@@ -2806,7 +4382,7 @@
       </c>
       <c r="B102" s="6" t="n"/>
       <c r="C102" s="4">
-        <f>IFERROR(VLOOKUP(B102,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B102,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D102" s="7" t="n"/>
@@ -2821,7 +4397,7 @@
       </c>
       <c r="B103" s="6" t="n"/>
       <c r="C103" s="4">
-        <f>IFERROR(VLOOKUP(B103,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B103,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D103" s="7" t="n"/>
@@ -2836,7 +4412,7 @@
       </c>
       <c r="B104" s="6" t="n"/>
       <c r="C104" s="4">
-        <f>IFERROR(VLOOKUP(B104,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B104,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D104" s="7" t="n"/>
@@ -2851,7 +4427,7 @@
       </c>
       <c r="B105" s="6" t="n"/>
       <c r="C105" s="4">
-        <f>IFERROR(VLOOKUP(B105,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B105,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D105" s="7" t="n"/>
@@ -2866,7 +4442,7 @@
       </c>
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="4">
-        <f>IFERROR(VLOOKUP(B106,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B106,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D106" s="7" t="n"/>
@@ -2881,7 +4457,7 @@
       </c>
       <c r="B107" s="6" t="n"/>
       <c r="C107" s="4">
-        <f>IFERROR(VLOOKUP(B107,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B107,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D107" s="7" t="n"/>
@@ -2896,7 +4472,7 @@
       </c>
       <c r="B108" s="6" t="n"/>
       <c r="C108" s="4">
-        <f>IFERROR(VLOOKUP(B108,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B108,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D108" s="7" t="n"/>
@@ -2911,7 +4487,7 @@
       </c>
       <c r="B109" s="6" t="n"/>
       <c r="C109" s="4">
-        <f>IFERROR(VLOOKUP(B109,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B109,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D109" s="7" t="n"/>
@@ -2926,7 +4502,7 @@
       </c>
       <c r="B110" s="6" t="n"/>
       <c r="C110" s="4">
-        <f>IFERROR(VLOOKUP(B110,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B110,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D110" s="7" t="n"/>
@@ -2941,7 +4517,7 @@
       </c>
       <c r="B111" s="6" t="n"/>
       <c r="C111" s="4">
-        <f>IFERROR(VLOOKUP(B111,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B111,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D111" s="7" t="n"/>
@@ -2956,7 +4532,7 @@
       </c>
       <c r="B112" s="6" t="n"/>
       <c r="C112" s="4">
-        <f>IFERROR(VLOOKUP(B112,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B112,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D112" s="7" t="n"/>
@@ -2971,7 +4547,7 @@
       </c>
       <c r="B113" s="6" t="n"/>
       <c r="C113" s="4">
-        <f>IFERROR(VLOOKUP(B113,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B113,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D113" s="7" t="n"/>
@@ -2986,7 +4562,7 @@
       </c>
       <c r="B114" s="6" t="n"/>
       <c r="C114" s="4">
-        <f>IFERROR(VLOOKUP(B114,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B114,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D114" s="7" t="n"/>
@@ -3001,7 +4577,7 @@
       </c>
       <c r="B115" s="6" t="n"/>
       <c r="C115" s="4">
-        <f>IFERROR(VLOOKUP(B115,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B115,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D115" s="7" t="n"/>
@@ -3016,7 +4592,7 @@
       </c>
       <c r="B116" s="6" t="n"/>
       <c r="C116" s="4">
-        <f>IFERROR(VLOOKUP(B116,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B116,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D116" s="7" t="n"/>
@@ -3031,7 +4607,7 @@
       </c>
       <c r="B117" s="6" t="n"/>
       <c r="C117" s="4">
-        <f>IFERROR(VLOOKUP(B117,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B117,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D117" s="7" t="n"/>
@@ -3046,7 +4622,7 @@
       </c>
       <c r="B118" s="6" t="n"/>
       <c r="C118" s="4">
-        <f>IFERROR(VLOOKUP(B118,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B118,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D118" s="7" t="n"/>
@@ -3061,7 +4637,7 @@
       </c>
       <c r="B119" s="6" t="n"/>
       <c r="C119" s="4">
-        <f>IFERROR(VLOOKUP(B119,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B119,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D119" s="7" t="n"/>
@@ -3076,7 +4652,7 @@
       </c>
       <c r="B120" s="6" t="n"/>
       <c r="C120" s="4">
-        <f>IFERROR(VLOOKUP(B120,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B120,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D120" s="7" t="n"/>
@@ -3091,7 +4667,7 @@
       </c>
       <c r="B121" s="6" t="n"/>
       <c r="C121" s="4">
-        <f>IFERROR(VLOOKUP(B121,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B121,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D121" s="7" t="n"/>
@@ -3106,7 +4682,7 @@
       </c>
       <c r="B122" s="6" t="n"/>
       <c r="C122" s="4">
-        <f>IFERROR(VLOOKUP(B122,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B122,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D122" s="7" t="n"/>
@@ -3121,7 +4697,7 @@
       </c>
       <c r="B123" s="6" t="n"/>
       <c r="C123" s="4">
-        <f>IFERROR(VLOOKUP(B123,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B123,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D123" s="7" t="n"/>
@@ -3136,7 +4712,7 @@
       </c>
       <c r="B124" s="6" t="n"/>
       <c r="C124" s="4">
-        <f>IFERROR(VLOOKUP(B124,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B124,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D124" s="7" t="n"/>
@@ -3151,7 +4727,7 @@
       </c>
       <c r="B125" s="6" t="n"/>
       <c r="C125" s="4">
-        <f>IFERROR(VLOOKUP(B125,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B125,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D125" s="7" t="n"/>
@@ -3166,7 +4742,7 @@
       </c>
       <c r="B126" s="6" t="n"/>
       <c r="C126" s="4">
-        <f>IFERROR(VLOOKUP(B126,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B126,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D126" s="7" t="n"/>
@@ -3181,7 +4757,7 @@
       </c>
       <c r="B127" s="6" t="n"/>
       <c r="C127" s="4">
-        <f>IFERROR(VLOOKUP(B127,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B127,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D127" s="7" t="n"/>
@@ -3196,7 +4772,7 @@
       </c>
       <c r="B128" s="6" t="n"/>
       <c r="C128" s="4">
-        <f>IFERROR(VLOOKUP(B128,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B128,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D128" s="7" t="n"/>
@@ -3211,7 +4787,7 @@
       </c>
       <c r="B129" s="6" t="n"/>
       <c r="C129" s="4">
-        <f>IFERROR(VLOOKUP(B129,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B129,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D129" s="7" t="n"/>
@@ -3226,7 +4802,7 @@
       </c>
       <c r="B130" s="6" t="n"/>
       <c r="C130" s="4">
-        <f>IFERROR(VLOOKUP(B130,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B130,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D130" s="7" t="n"/>
@@ -3241,7 +4817,7 @@
       </c>
       <c r="B131" s="6" t="n"/>
       <c r="C131" s="4">
-        <f>IFERROR(VLOOKUP(B131,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B131,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D131" s="7" t="n"/>
@@ -3256,7 +4832,7 @@
       </c>
       <c r="B132" s="6" t="n"/>
       <c r="C132" s="4">
-        <f>IFERROR(VLOOKUP(B132,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B132,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D132" s="7" t="n"/>
@@ -3271,7 +4847,7 @@
       </c>
       <c r="B133" s="6" t="n"/>
       <c r="C133" s="4">
-        <f>IFERROR(VLOOKUP(B133,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B133,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D133" s="7" t="n"/>
@@ -3286,7 +4862,7 @@
       </c>
       <c r="B134" s="6" t="n"/>
       <c r="C134" s="4">
-        <f>IFERROR(VLOOKUP(B134,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B134,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D134" s="7" t="n"/>
@@ -3301,7 +4877,7 @@
       </c>
       <c r="B135" s="6" t="n"/>
       <c r="C135" s="4">
-        <f>IFERROR(VLOOKUP(B135,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B135,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D135" s="7" t="n"/>
@@ -3316,7 +4892,7 @@
       </c>
       <c r="B136" s="6" t="n"/>
       <c r="C136" s="4">
-        <f>IFERROR(VLOOKUP(B136,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B136,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D136" s="7" t="n"/>
@@ -3331,7 +4907,7 @@
       </c>
       <c r="B137" s="6" t="n"/>
       <c r="C137" s="4">
-        <f>IFERROR(VLOOKUP(B137,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B137,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D137" s="7" t="n"/>
@@ -3346,7 +4922,7 @@
       </c>
       <c r="B138" s="6" t="n"/>
       <c r="C138" s="4">
-        <f>IFERROR(VLOOKUP(B138,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B138,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D138" s="7" t="n"/>
@@ -3361,7 +4937,7 @@
       </c>
       <c r="B139" s="6" t="n"/>
       <c r="C139" s="4">
-        <f>IFERROR(VLOOKUP(B139,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B139,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D139" s="7" t="n"/>
@@ -3376,7 +4952,7 @@
       </c>
       <c r="B140" s="6" t="n"/>
       <c r="C140" s="4">
-        <f>IFERROR(VLOOKUP(B140,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B140,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D140" s="7" t="n"/>
@@ -3391,7 +4967,7 @@
       </c>
       <c r="B141" s="6" t="n"/>
       <c r="C141" s="4">
-        <f>IFERROR(VLOOKUP(B141,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B141,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D141" s="7" t="n"/>
@@ -3406,7 +4982,7 @@
       </c>
       <c r="B142" s="6" t="n"/>
       <c r="C142" s="4">
-        <f>IFERROR(VLOOKUP(B142,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B142,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D142" s="7" t="n"/>
@@ -3421,7 +4997,7 @@
       </c>
       <c r="B143" s="6" t="n"/>
       <c r="C143" s="4">
-        <f>IFERROR(VLOOKUP(B143,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B143,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D143" s="7" t="n"/>
@@ -3436,7 +5012,7 @@
       </c>
       <c r="B144" s="6" t="n"/>
       <c r="C144" s="4">
-        <f>IFERROR(VLOOKUP(B144,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B144,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D144" s="7" t="n"/>
@@ -3451,7 +5027,7 @@
       </c>
       <c r="B145" s="6" t="n"/>
       <c r="C145" s="4">
-        <f>IFERROR(VLOOKUP(B145,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B145,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D145" s="7" t="n"/>
@@ -3466,7 +5042,7 @@
       </c>
       <c r="B146" s="6" t="n"/>
       <c r="C146" s="4">
-        <f>IFERROR(VLOOKUP(B146,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B146,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D146" s="7" t="n"/>
@@ -3481,7 +5057,7 @@
       </c>
       <c r="B147" s="6" t="n"/>
       <c r="C147" s="4">
-        <f>IFERROR(VLOOKUP(B147,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B147,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D147" s="7" t="n"/>
@@ -3496,7 +5072,7 @@
       </c>
       <c r="B148" s="6" t="n"/>
       <c r="C148" s="4">
-        <f>IFERROR(VLOOKUP(B148,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B148,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D148" s="7" t="n"/>
@@ -3511,7 +5087,7 @@
       </c>
       <c r="B149" s="6" t="n"/>
       <c r="C149" s="4">
-        <f>IFERROR(VLOOKUP(B149,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B149,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D149" s="7" t="n"/>
@@ -3526,7 +5102,7 @@
       </c>
       <c r="B150" s="6" t="n"/>
       <c r="C150" s="4">
-        <f>IFERROR(VLOOKUP(B150,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B150,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D150" s="7" t="n"/>
@@ -3541,7 +5117,7 @@
       </c>
       <c r="B151" s="6" t="n"/>
       <c r="C151" s="4">
-        <f>IFERROR(VLOOKUP(B151,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B151,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D151" s="7" t="n"/>
@@ -3556,7 +5132,7 @@
       </c>
       <c r="B152" s="6" t="n"/>
       <c r="C152" s="4">
-        <f>IFERROR(VLOOKUP(B152,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B152,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D152" s="7" t="n"/>
@@ -3571,7 +5147,7 @@
       </c>
       <c r="B153" s="6" t="n"/>
       <c r="C153" s="4">
-        <f>IFERROR(VLOOKUP(B153,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B153,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D153" s="7" t="n"/>
@@ -3586,7 +5162,7 @@
       </c>
       <c r="B154" s="6" t="n"/>
       <c r="C154" s="4">
-        <f>IFERROR(VLOOKUP(B154,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B154,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D154" s="7" t="n"/>
@@ -3601,7 +5177,7 @@
       </c>
       <c r="B155" s="6" t="n"/>
       <c r="C155" s="4">
-        <f>IFERROR(VLOOKUP(B155,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B155,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D155" s="7" t="n"/>
@@ -3616,7 +5192,7 @@
       </c>
       <c r="B156" s="6" t="n"/>
       <c r="C156" s="4">
-        <f>IFERROR(VLOOKUP(B156,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B156,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D156" s="7" t="n"/>
@@ -3631,7 +5207,7 @@
       </c>
       <c r="B157" s="6" t="n"/>
       <c r="C157" s="4">
-        <f>IFERROR(VLOOKUP(B157,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B157,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D157" s="7" t="n"/>
@@ -3646,7 +5222,7 @@
       </c>
       <c r="B158" s="6" t="n"/>
       <c r="C158" s="4">
-        <f>IFERROR(VLOOKUP(B158,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B158,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D158" s="7" t="n"/>
@@ -3661,7 +5237,7 @@
       </c>
       <c r="B159" s="6" t="n"/>
       <c r="C159" s="4">
-        <f>IFERROR(VLOOKUP(B159,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B159,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D159" s="7" t="n"/>
@@ -3676,7 +5252,7 @@
       </c>
       <c r="B160" s="6" t="n"/>
       <c r="C160" s="4">
-        <f>IFERROR(VLOOKUP(B160,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B160,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D160" s="7" t="n"/>
@@ -3691,7 +5267,7 @@
       </c>
       <c r="B161" s="6" t="n"/>
       <c r="C161" s="4">
-        <f>IFERROR(VLOOKUP(B161,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B161,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D161" s="7" t="n"/>
@@ -3706,7 +5282,7 @@
       </c>
       <c r="B162" s="6" t="n"/>
       <c r="C162" s="4">
-        <f>IFERROR(VLOOKUP(B162,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B162,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D162" s="7" t="n"/>
@@ -3721,7 +5297,7 @@
       </c>
       <c r="B163" s="6" t="n"/>
       <c r="C163" s="4">
-        <f>IFERROR(VLOOKUP(B163,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B163,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D163" s="7" t="n"/>
@@ -3736,7 +5312,7 @@
       </c>
       <c r="B164" s="6" t="n"/>
       <c r="C164" s="4">
-        <f>IFERROR(VLOOKUP(B164,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B164,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D164" s="7" t="n"/>
@@ -3751,7 +5327,7 @@
       </c>
       <c r="B165" s="6" t="n"/>
       <c r="C165" s="4">
-        <f>IFERROR(VLOOKUP(B165,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B165,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D165" s="7" t="n"/>
@@ -3766,7 +5342,7 @@
       </c>
       <c r="B166" s="6" t="n"/>
       <c r="C166" s="4">
-        <f>IFERROR(VLOOKUP(B166,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B166,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D166" s="7" t="n"/>
@@ -3781,7 +5357,7 @@
       </c>
       <c r="B167" s="6" t="n"/>
       <c r="C167" s="4">
-        <f>IFERROR(VLOOKUP(B167,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B167,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D167" s="7" t="n"/>
@@ -3796,7 +5372,7 @@
       </c>
       <c r="B168" s="6" t="n"/>
       <c r="C168" s="4">
-        <f>IFERROR(VLOOKUP(B168,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B168,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D168" s="7" t="n"/>
@@ -3811,7 +5387,7 @@
       </c>
       <c r="B169" s="6" t="n"/>
       <c r="C169" s="4">
-        <f>IFERROR(VLOOKUP(B169,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B169,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D169" s="7" t="n"/>
@@ -3826,7 +5402,7 @@
       </c>
       <c r="B170" s="6" t="n"/>
       <c r="C170" s="4">
-        <f>IFERROR(VLOOKUP(B170,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B170,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D170" s="7" t="n"/>
@@ -3841,7 +5417,7 @@
       </c>
       <c r="B171" s="6" t="n"/>
       <c r="C171" s="4">
-        <f>IFERROR(VLOOKUP(B171,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B171,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D171" s="7" t="n"/>
@@ -3856,7 +5432,7 @@
       </c>
       <c r="B172" s="6" t="n"/>
       <c r="C172" s="4">
-        <f>IFERROR(VLOOKUP(B172,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B172,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D172" s="7" t="n"/>
@@ -3871,7 +5447,7 @@
       </c>
       <c r="B173" s="6" t="n"/>
       <c r="C173" s="4">
-        <f>IFERROR(VLOOKUP(B173,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B173,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D173" s="7" t="n"/>
@@ -3886,7 +5462,7 @@
       </c>
       <c r="B174" s="6" t="n"/>
       <c r="C174" s="4">
-        <f>IFERROR(VLOOKUP(B174,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B174,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D174" s="7" t="n"/>
@@ -3901,7 +5477,7 @@
       </c>
       <c r="B175" s="6" t="n"/>
       <c r="C175" s="4">
-        <f>IFERROR(VLOOKUP(B175,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B175,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D175" s="7" t="n"/>
@@ -3916,7 +5492,7 @@
       </c>
       <c r="B176" s="6" t="n"/>
       <c r="C176" s="4">
-        <f>IFERROR(VLOOKUP(B176,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B176,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D176" s="7" t="n"/>
@@ -3931,7 +5507,7 @@
       </c>
       <c r="B177" s="6" t="n"/>
       <c r="C177" s="4">
-        <f>IFERROR(VLOOKUP(B177,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B177,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D177" s="7" t="n"/>
@@ -3946,7 +5522,7 @@
       </c>
       <c r="B178" s="6" t="n"/>
       <c r="C178" s="4">
-        <f>IFERROR(VLOOKUP(B178,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B178,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D178" s="7" t="n"/>
@@ -3961,7 +5537,7 @@
       </c>
       <c r="B179" s="6" t="n"/>
       <c r="C179" s="4">
-        <f>IFERROR(VLOOKUP(B179,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B179,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D179" s="7" t="n"/>
@@ -3976,7 +5552,7 @@
       </c>
       <c r="B180" s="6" t="n"/>
       <c r="C180" s="4">
-        <f>IFERROR(VLOOKUP(B180,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B180,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D180" s="7" t="n"/>
@@ -3991,7 +5567,7 @@
       </c>
       <c r="B181" s="6" t="n"/>
       <c r="C181" s="4">
-        <f>IFERROR(VLOOKUP(B181,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B181,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D181" s="7" t="n"/>
@@ -4006,7 +5582,7 @@
       </c>
       <c r="B182" s="6" t="n"/>
       <c r="C182" s="4">
-        <f>IFERROR(VLOOKUP(B182,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B182,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D182" s="7" t="n"/>
@@ -4021,7 +5597,7 @@
       </c>
       <c r="B183" s="6" t="n"/>
       <c r="C183" s="4">
-        <f>IFERROR(VLOOKUP(B183,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B183,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D183" s="7" t="n"/>
@@ -4036,7 +5612,7 @@
       </c>
       <c r="B184" s="6" t="n"/>
       <c r="C184" s="4">
-        <f>IFERROR(VLOOKUP(B184,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B184,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D184" s="7" t="n"/>
@@ -4051,7 +5627,7 @@
       </c>
       <c r="B185" s="6" t="n"/>
       <c r="C185" s="4">
-        <f>IFERROR(VLOOKUP(B185,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B185,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D185" s="7" t="n"/>
@@ -4066,7 +5642,7 @@
       </c>
       <c r="B186" s="6" t="n"/>
       <c r="C186" s="4">
-        <f>IFERROR(VLOOKUP(B186,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B186,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D186" s="7" t="n"/>
@@ -4081,7 +5657,7 @@
       </c>
       <c r="B187" s="6" t="n"/>
       <c r="C187" s="4">
-        <f>IFERROR(VLOOKUP(B187,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B187,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D187" s="7" t="n"/>
@@ -4096,7 +5672,7 @@
       </c>
       <c r="B188" s="6" t="n"/>
       <c r="C188" s="4">
-        <f>IFERROR(VLOOKUP(B188,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B188,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D188" s="7" t="n"/>
@@ -4111,7 +5687,7 @@
       </c>
       <c r="B189" s="6" t="n"/>
       <c r="C189" s="4">
-        <f>IFERROR(VLOOKUP(B189,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B189,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D189" s="7" t="n"/>
@@ -4126,7 +5702,7 @@
       </c>
       <c r="B190" s="6" t="n"/>
       <c r="C190" s="4">
-        <f>IFERROR(VLOOKUP(B190,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B190,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D190" s="7" t="n"/>
@@ -4141,7 +5717,7 @@
       </c>
       <c r="B191" s="6" t="n"/>
       <c r="C191" s="4">
-        <f>IFERROR(VLOOKUP(B191,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B191,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D191" s="7" t="n"/>
@@ -4156,7 +5732,7 @@
       </c>
       <c r="B192" s="6" t="n"/>
       <c r="C192" s="4">
-        <f>IFERROR(VLOOKUP(B192,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B192,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D192" s="7" t="n"/>
@@ -4171,7 +5747,7 @@
       </c>
       <c r="B193" s="6" t="n"/>
       <c r="C193" s="4">
-        <f>IFERROR(VLOOKUP(B193,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B193,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D193" s="7" t="n"/>
@@ -4186,7 +5762,7 @@
       </c>
       <c r="B194" s="6" t="n"/>
       <c r="C194" s="4">
-        <f>IFERROR(VLOOKUP(B194,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B194,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D194" s="7" t="n"/>
@@ -4201,7 +5777,7 @@
       </c>
       <c r="B195" s="6" t="n"/>
       <c r="C195" s="4">
-        <f>IFERROR(VLOOKUP(B195,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B195,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D195" s="7" t="n"/>
@@ -4216,7 +5792,7 @@
       </c>
       <c r="B196" s="6" t="n"/>
       <c r="C196" s="4">
-        <f>IFERROR(VLOOKUP(B196,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B196,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D196" s="7" t="n"/>
@@ -4231,7 +5807,7 @@
       </c>
       <c r="B197" s="6" t="n"/>
       <c r="C197" s="4">
-        <f>IFERROR(VLOOKUP(B197,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B197,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D197" s="7" t="n"/>
@@ -4246,7 +5822,7 @@
       </c>
       <c r="B198" s="6" t="n"/>
       <c r="C198" s="4">
-        <f>IFERROR(VLOOKUP(B198,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B198,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D198" s="7" t="n"/>
@@ -4261,7 +5837,7 @@
       </c>
       <c r="B199" s="6" t="n"/>
       <c r="C199" s="4">
-        <f>IFERROR(VLOOKUP(B199,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B199,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D199" s="7" t="n"/>
@@ -4276,7 +5852,7 @@
       </c>
       <c r="B200" s="6" t="n"/>
       <c r="C200" s="4">
-        <f>IFERROR(VLOOKUP(B200,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B200,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D200" s="7" t="n"/>
@@ -4291,7 +5867,7 @@
       </c>
       <c r="B201" s="6" t="n"/>
       <c r="C201" s="4">
-        <f>IFERROR(VLOOKUP(B201,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B201,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D201" s="7" t="n"/>
@@ -4306,7 +5882,7 @@
       </c>
       <c r="B202" s="6" t="n"/>
       <c r="C202" s="4">
-        <f>IFERROR(VLOOKUP(B202,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B202,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D202" s="7" t="n"/>
@@ -4321,7 +5897,7 @@
       </c>
       <c r="B203" s="6" t="n"/>
       <c r="C203" s="4">
-        <f>IFERROR(VLOOKUP(B203,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B203,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D203" s="7" t="n"/>
@@ -4336,7 +5912,7 @@
       </c>
       <c r="B204" s="6" t="n"/>
       <c r="C204" s="4">
-        <f>IFERROR(VLOOKUP(B204,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B204,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D204" s="7" t="n"/>
@@ -4351,7 +5927,7 @@
       </c>
       <c r="B205" s="6" t="n"/>
       <c r="C205" s="4">
-        <f>IFERROR(VLOOKUP(B205,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B205,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D205" s="7" t="n"/>
@@ -4366,7 +5942,7 @@
       </c>
       <c r="B206" s="6" t="n"/>
       <c r="C206" s="4">
-        <f>IFERROR(VLOOKUP(B206,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B206,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D206" s="7" t="n"/>
@@ -4381,7 +5957,7 @@
       </c>
       <c r="B207" s="6" t="n"/>
       <c r="C207" s="4">
-        <f>IFERROR(VLOOKUP(B207,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B207,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D207" s="7" t="n"/>
@@ -4396,7 +5972,7 @@
       </c>
       <c r="B208" s="6" t="n"/>
       <c r="C208" s="4">
-        <f>IFERROR(VLOOKUP(B208,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B208,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D208" s="7" t="n"/>
@@ -4411,7 +5987,7 @@
       </c>
       <c r="B209" s="6" t="n"/>
       <c r="C209" s="4">
-        <f>IFERROR(VLOOKUP(B209,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B209,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D209" s="7" t="n"/>
@@ -4426,7 +6002,7 @@
       </c>
       <c r="B210" s="6" t="n"/>
       <c r="C210" s="4">
-        <f>IFERROR(VLOOKUP(B210,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B210,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D210" s="7" t="n"/>
@@ -4441,7 +6017,7 @@
       </c>
       <c r="B211" s="6" t="n"/>
       <c r="C211" s="4">
-        <f>IFERROR(VLOOKUP(B211,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B211,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D211" s="7" t="n"/>
@@ -4456,7 +6032,7 @@
       </c>
       <c r="B212" s="6" t="n"/>
       <c r="C212" s="4">
-        <f>IFERROR(VLOOKUP(B212,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B212,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D212" s="7" t="n"/>
@@ -4471,7 +6047,7 @@
       </c>
       <c r="B213" s="6" t="n"/>
       <c r="C213" s="4">
-        <f>IFERROR(VLOOKUP(B213,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B213,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D213" s="7" t="n"/>
@@ -4486,7 +6062,7 @@
       </c>
       <c r="B214" s="6" t="n"/>
       <c r="C214" s="4">
-        <f>IFERROR(VLOOKUP(B214,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B214,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D214" s="7" t="n"/>
@@ -4501,7 +6077,7 @@
       </c>
       <c r="B215" s="6" t="n"/>
       <c r="C215" s="4">
-        <f>IFERROR(VLOOKUP(B215,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B215,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D215" s="7" t="n"/>
@@ -4516,7 +6092,7 @@
       </c>
       <c r="B216" s="6" t="n"/>
       <c r="C216" s="4">
-        <f>IFERROR(VLOOKUP(B216,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B216,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D216" s="7" t="n"/>
@@ -4531,7 +6107,7 @@
       </c>
       <c r="B217" s="6" t="n"/>
       <c r="C217" s="4">
-        <f>IFERROR(VLOOKUP(B217,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B217,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D217" s="7" t="n"/>
@@ -4546,7 +6122,7 @@
       </c>
       <c r="B218" s="6" t="n"/>
       <c r="C218" s="4">
-        <f>IFERROR(VLOOKUP(B218,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B218,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D218" s="7" t="n"/>
@@ -4561,7 +6137,7 @@
       </c>
       <c r="B219" s="6" t="n"/>
       <c r="C219" s="4">
-        <f>IFERROR(VLOOKUP(B219,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B219,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D219" s="7" t="n"/>
@@ -4576,7 +6152,7 @@
       </c>
       <c r="B220" s="6" t="n"/>
       <c r="C220" s="4">
-        <f>IFERROR(VLOOKUP(B220,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B220,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D220" s="7" t="n"/>
@@ -4591,7 +6167,7 @@
       </c>
       <c r="B221" s="6" t="n"/>
       <c r="C221" s="4">
-        <f>IFERROR(VLOOKUP(B221,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B221,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D221" s="7" t="n"/>
@@ -4606,7 +6182,7 @@
       </c>
       <c r="B222" s="6" t="n"/>
       <c r="C222" s="4">
-        <f>IFERROR(VLOOKUP(B222,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B222,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D222" s="7" t="n"/>
@@ -4621,7 +6197,7 @@
       </c>
       <c r="B223" s="6" t="n"/>
       <c r="C223" s="4">
-        <f>IFERROR(VLOOKUP(B223,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B223,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D223" s="7" t="n"/>
@@ -4636,7 +6212,7 @@
       </c>
       <c r="B224" s="6" t="n"/>
       <c r="C224" s="4">
-        <f>IFERROR(VLOOKUP(B224,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B224,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D224" s="7" t="n"/>
@@ -4651,7 +6227,7 @@
       </c>
       <c r="B225" s="6" t="n"/>
       <c r="C225" s="4">
-        <f>IFERROR(VLOOKUP(B225,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B225,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D225" s="7" t="n"/>
@@ -4666,7 +6242,7 @@
       </c>
       <c r="B226" s="6" t="n"/>
       <c r="C226" s="4">
-        <f>IFERROR(VLOOKUP(B226,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B226,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D226" s="7" t="n"/>
@@ -4681,7 +6257,7 @@
       </c>
       <c r="B227" s="6" t="n"/>
       <c r="C227" s="4">
-        <f>IFERROR(VLOOKUP(B227,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B227,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D227" s="7" t="n"/>
@@ -4696,7 +6272,7 @@
       </c>
       <c r="B228" s="6" t="n"/>
       <c r="C228" s="4">
-        <f>IFERROR(VLOOKUP(B228,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B228,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D228" s="7" t="n"/>
@@ -4711,7 +6287,7 @@
       </c>
       <c r="B229" s="6" t="n"/>
       <c r="C229" s="4">
-        <f>IFERROR(VLOOKUP(B229,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B229,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D229" s="7" t="n"/>
@@ -4726,7 +6302,7 @@
       </c>
       <c r="B230" s="6" t="n"/>
       <c r="C230" s="4">
-        <f>IFERROR(VLOOKUP(B230,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B230,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D230" s="7" t="n"/>
@@ -4741,7 +6317,7 @@
       </c>
       <c r="B231" s="6" t="n"/>
       <c r="C231" s="4">
-        <f>IFERROR(VLOOKUP(B231,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B231,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D231" s="7" t="n"/>
@@ -4756,7 +6332,7 @@
       </c>
       <c r="B232" s="6" t="n"/>
       <c r="C232" s="4">
-        <f>IFERROR(VLOOKUP(B232,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B232,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D232" s="7" t="n"/>
@@ -4771,7 +6347,7 @@
       </c>
       <c r="B233" s="6" t="n"/>
       <c r="C233" s="4">
-        <f>IFERROR(VLOOKUP(B233,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B233,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D233" s="7" t="n"/>
@@ -4786,7 +6362,7 @@
       </c>
       <c r="B234" s="6" t="n"/>
       <c r="C234" s="4">
-        <f>IFERROR(VLOOKUP(B234,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B234,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D234" s="7" t="n"/>
@@ -4801,7 +6377,7 @@
       </c>
       <c r="B235" s="6" t="n"/>
       <c r="C235" s="4">
-        <f>IFERROR(VLOOKUP(B235,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B235,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D235" s="7" t="n"/>
@@ -4816,7 +6392,7 @@
       </c>
       <c r="B236" s="6" t="n"/>
       <c r="C236" s="4">
-        <f>IFERROR(VLOOKUP(B236,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B236,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D236" s="7" t="n"/>
@@ -4831,7 +6407,7 @@
       </c>
       <c r="B237" s="6" t="n"/>
       <c r="C237" s="4">
-        <f>IFERROR(VLOOKUP(B237,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B237,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D237" s="7" t="n"/>
@@ -4846,7 +6422,7 @@
       </c>
       <c r="B238" s="6" t="n"/>
       <c r="C238" s="4">
-        <f>IFERROR(VLOOKUP(B238,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B238,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D238" s="7" t="n"/>
@@ -4861,7 +6437,7 @@
       </c>
       <c r="B239" s="6" t="n"/>
       <c r="C239" s="4">
-        <f>IFERROR(VLOOKUP(B239,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B239,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D239" s="7" t="n"/>
@@ -4876,7 +6452,7 @@
       </c>
       <c r="B240" s="6" t="n"/>
       <c r="C240" s="4">
-        <f>IFERROR(VLOOKUP(B240,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B240,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D240" s="7" t="n"/>
@@ -4891,7 +6467,7 @@
       </c>
       <c r="B241" s="6" t="n"/>
       <c r="C241" s="4">
-        <f>IFERROR(VLOOKUP(B241,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B241,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D241" s="7" t="n"/>
@@ -4906,7 +6482,7 @@
       </c>
       <c r="B242" s="6" t="n"/>
       <c r="C242" s="4">
-        <f>IFERROR(VLOOKUP(B242,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B242,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D242" s="7" t="n"/>
@@ -4921,7 +6497,7 @@
       </c>
       <c r="B243" s="6" t="n"/>
       <c r="C243" s="4">
-        <f>IFERROR(VLOOKUP(B243,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B243,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D243" s="7" t="n"/>
@@ -4936,7 +6512,7 @@
       </c>
       <c r="B244" s="6" t="n"/>
       <c r="C244" s="4">
-        <f>IFERROR(VLOOKUP(B244,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B244,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D244" s="7" t="n"/>
@@ -4951,7 +6527,7 @@
       </c>
       <c r="B245" s="6" t="n"/>
       <c r="C245" s="4">
-        <f>IFERROR(VLOOKUP(B245,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B245,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D245" s="7" t="n"/>
@@ -4966,7 +6542,7 @@
       </c>
       <c r="B246" s="6" t="n"/>
       <c r="C246" s="4">
-        <f>IFERROR(VLOOKUP(B246,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B246,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D246" s="7" t="n"/>
@@ -4981,7 +6557,7 @@
       </c>
       <c r="B247" s="6" t="n"/>
       <c r="C247" s="4">
-        <f>IFERROR(VLOOKUP(B247,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B247,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D247" s="7" t="n"/>
@@ -4996,7 +6572,7 @@
       </c>
       <c r="B248" s="6" t="n"/>
       <c r="C248" s="4">
-        <f>IFERROR(VLOOKUP(B248,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B248,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D248" s="7" t="n"/>
@@ -5011,7 +6587,7 @@
       </c>
       <c r="B249" s="6" t="n"/>
       <c r="C249" s="4">
-        <f>IFERROR(VLOOKUP(B249,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B249,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D249" s="7" t="n"/>
@@ -5026,7 +6602,7 @@
       </c>
       <c r="B250" s="6" t="n"/>
       <c r="C250" s="4">
-        <f>IFERROR(VLOOKUP(B250,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B250,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D250" s="7" t="n"/>
@@ -5041,7 +6617,7 @@
       </c>
       <c r="B251" s="6" t="n"/>
       <c r="C251" s="4">
-        <f>IFERROR(VLOOKUP(B251,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B251,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D251" s="7" t="n"/>
@@ -5056,7 +6632,7 @@
       </c>
       <c r="B252" s="6" t="n"/>
       <c r="C252" s="4">
-        <f>IFERROR(VLOOKUP(B252,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B252,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D252" s="7" t="n"/>
@@ -5071,7 +6647,7 @@
       </c>
       <c r="B253" s="6" t="n"/>
       <c r="C253" s="4">
-        <f>IFERROR(VLOOKUP(B253,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B253,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D253" s="7" t="n"/>
@@ -5086,7 +6662,7 @@
       </c>
       <c r="B254" s="6" t="n"/>
       <c r="C254" s="4">
-        <f>IFERROR(VLOOKUP(B254,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B254,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D254" s="7" t="n"/>
@@ -5101,7 +6677,7 @@
       </c>
       <c r="B255" s="6" t="n"/>
       <c r="C255" s="4">
-        <f>IFERROR(VLOOKUP(B255,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B255,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D255" s="7" t="n"/>
@@ -5116,7 +6692,7 @@
       </c>
       <c r="B256" s="6" t="n"/>
       <c r="C256" s="4">
-        <f>IFERROR(VLOOKUP(B256,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B256,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D256" s="7" t="n"/>
@@ -5131,7 +6707,7 @@
       </c>
       <c r="B257" s="6" t="n"/>
       <c r="C257" s="4">
-        <f>IFERROR(VLOOKUP(B257,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B257,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D257" s="7" t="n"/>
@@ -5146,7 +6722,7 @@
       </c>
       <c r="B258" s="6" t="n"/>
       <c r="C258" s="4">
-        <f>IFERROR(VLOOKUP(B258,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B258,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D258" s="7" t="n"/>
@@ -5161,7 +6737,7 @@
       </c>
       <c r="B259" s="6" t="n"/>
       <c r="C259" s="4">
-        <f>IFERROR(VLOOKUP(B259,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B259,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D259" s="7" t="n"/>
@@ -5176,7 +6752,7 @@
       </c>
       <c r="B260" s="6" t="n"/>
       <c r="C260" s="4">
-        <f>IFERROR(VLOOKUP(B260,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B260,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D260" s="7" t="n"/>
@@ -5191,7 +6767,7 @@
       </c>
       <c r="B261" s="6" t="n"/>
       <c r="C261" s="4">
-        <f>IFERROR(VLOOKUP(B261,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B261,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D261" s="7" t="n"/>
@@ -5206,7 +6782,7 @@
       </c>
       <c r="B262" s="6" t="n"/>
       <c r="C262" s="4">
-        <f>IFERROR(VLOOKUP(B262,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B262,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D262" s="7" t="n"/>
@@ -5221,7 +6797,7 @@
       </c>
       <c r="B263" s="6" t="n"/>
       <c r="C263" s="4">
-        <f>IFERROR(VLOOKUP(B263,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B263,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D263" s="7" t="n"/>
@@ -5236,7 +6812,7 @@
       </c>
       <c r="B264" s="6" t="n"/>
       <c r="C264" s="4">
-        <f>IFERROR(VLOOKUP(B264,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B264,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D264" s="7" t="n"/>
@@ -5251,7 +6827,7 @@
       </c>
       <c r="B265" s="6" t="n"/>
       <c r="C265" s="4">
-        <f>IFERROR(VLOOKUP(B265,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B265,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D265" s="7" t="n"/>
@@ -5266,7 +6842,7 @@
       </c>
       <c r="B266" s="6" t="n"/>
       <c r="C266" s="4">
-        <f>IFERROR(VLOOKUP(B266,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B266,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D266" s="7" t="n"/>
@@ -5281,7 +6857,7 @@
       </c>
       <c r="B267" s="6" t="n"/>
       <c r="C267" s="4">
-        <f>IFERROR(VLOOKUP(B267,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B267,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D267" s="7" t="n"/>
@@ -5296,7 +6872,7 @@
       </c>
       <c r="B268" s="6" t="n"/>
       <c r="C268" s="4">
-        <f>IFERROR(VLOOKUP(B268,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B268,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D268" s="7" t="n"/>
@@ -5311,7 +6887,7 @@
       </c>
       <c r="B269" s="6" t="n"/>
       <c r="C269" s="4">
-        <f>IFERROR(VLOOKUP(B269,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B269,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D269" s="7" t="n"/>
@@ -5326,7 +6902,7 @@
       </c>
       <c r="B270" s="6" t="n"/>
       <c r="C270" s="4">
-        <f>IFERROR(VLOOKUP(B270,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B270,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D270" s="7" t="n"/>
@@ -5341,7 +6917,7 @@
       </c>
       <c r="B271" s="6" t="n"/>
       <c r="C271" s="4">
-        <f>IFERROR(VLOOKUP(B271,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B271,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D271" s="7" t="n"/>
@@ -5356,7 +6932,7 @@
       </c>
       <c r="B272" s="6" t="n"/>
       <c r="C272" s="4">
-        <f>IFERROR(VLOOKUP(B272,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B272,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D272" s="7" t="n"/>
@@ -5371,7 +6947,7 @@
       </c>
       <c r="B273" s="6" t="n"/>
       <c r="C273" s="4">
-        <f>IFERROR(VLOOKUP(B273,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B273,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D273" s="7" t="n"/>
@@ -5386,7 +6962,7 @@
       </c>
       <c r="B274" s="6" t="n"/>
       <c r="C274" s="4">
-        <f>IFERROR(VLOOKUP(B274,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B274,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D274" s="7" t="n"/>
@@ -5401,7 +6977,7 @@
       </c>
       <c r="B275" s="6" t="n"/>
       <c r="C275" s="4">
-        <f>IFERROR(VLOOKUP(B275,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B275,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D275" s="7" t="n"/>
@@ -5416,7 +6992,7 @@
       </c>
       <c r="B276" s="6" t="n"/>
       <c r="C276" s="4">
-        <f>IFERROR(VLOOKUP(B276,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B276,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D276" s="7" t="n"/>
@@ -5431,7 +7007,7 @@
       </c>
       <c r="B277" s="6" t="n"/>
       <c r="C277" s="4">
-        <f>IFERROR(VLOOKUP(B277,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B277,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D277" s="7" t="n"/>
@@ -5446,7 +7022,7 @@
       </c>
       <c r="B278" s="6" t="n"/>
       <c r="C278" s="4">
-        <f>IFERROR(VLOOKUP(B278,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B278,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D278" s="7" t="n"/>
@@ -5461,7 +7037,7 @@
       </c>
       <c r="B279" s="6" t="n"/>
       <c r="C279" s="4">
-        <f>IFERROR(VLOOKUP(B279,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B279,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D279" s="7" t="n"/>
@@ -5476,7 +7052,7 @@
       </c>
       <c r="B280" s="6" t="n"/>
       <c r="C280" s="4">
-        <f>IFERROR(VLOOKUP(B280,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B280,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D280" s="7" t="n"/>
@@ -5491,7 +7067,7 @@
       </c>
       <c r="B281" s="6" t="n"/>
       <c r="C281" s="4">
-        <f>IFERROR(VLOOKUP(B281,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B281,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D281" s="7" t="n"/>
@@ -5506,7 +7082,7 @@
       </c>
       <c r="B282" s="6" t="n"/>
       <c r="C282" s="4">
-        <f>IFERROR(VLOOKUP(B282,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B282,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D282" s="7" t="n"/>
@@ -5521,7 +7097,7 @@
       </c>
       <c r="B283" s="6" t="n"/>
       <c r="C283" s="4">
-        <f>IFERROR(VLOOKUP(B283,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B283,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D283" s="7" t="n"/>
@@ -5536,7 +7112,7 @@
       </c>
       <c r="B284" s="6" t="n"/>
       <c r="C284" s="4">
-        <f>IFERROR(VLOOKUP(B284,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B284,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D284" s="7" t="n"/>
@@ -5551,7 +7127,7 @@
       </c>
       <c r="B285" s="6" t="n"/>
       <c r="C285" s="4">
-        <f>IFERROR(VLOOKUP(B285,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B285,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D285" s="7" t="n"/>
@@ -5566,7 +7142,7 @@
       </c>
       <c r="B286" s="6" t="n"/>
       <c r="C286" s="4">
-        <f>IFERROR(VLOOKUP(B286,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B286,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D286" s="7" t="n"/>
@@ -5581,7 +7157,7 @@
       </c>
       <c r="B287" s="6" t="n"/>
       <c r="C287" s="4">
-        <f>IFERROR(VLOOKUP(B287,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B287,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D287" s="7" t="n"/>
@@ -5596,7 +7172,7 @@
       </c>
       <c r="B288" s="6" t="n"/>
       <c r="C288" s="4">
-        <f>IFERROR(VLOOKUP(B288,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B288,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D288" s="7" t="n"/>
@@ -5611,7 +7187,7 @@
       </c>
       <c r="B289" s="6" t="n"/>
       <c r="C289" s="4">
-        <f>IFERROR(VLOOKUP(B289,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B289,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D289" s="7" t="n"/>
@@ -5626,7 +7202,7 @@
       </c>
       <c r="B290" s="6" t="n"/>
       <c r="C290" s="4">
-        <f>IFERROR(VLOOKUP(B290,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B290,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D290" s="7" t="n"/>
@@ -5641,7 +7217,7 @@
       </c>
       <c r="B291" s="6" t="n"/>
       <c r="C291" s="4">
-        <f>IFERROR(VLOOKUP(B291,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B291,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D291" s="7" t="n"/>
@@ -5656,7 +7232,7 @@
       </c>
       <c r="B292" s="6" t="n"/>
       <c r="C292" s="4">
-        <f>IFERROR(VLOOKUP(B292,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B292,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D292" s="7" t="n"/>
@@ -5671,7 +7247,7 @@
       </c>
       <c r="B293" s="6" t="n"/>
       <c r="C293" s="4">
-        <f>IFERROR(VLOOKUP(B293,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B293,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D293" s="7" t="n"/>
@@ -5686,7 +7262,7 @@
       </c>
       <c r="B294" s="6" t="n"/>
       <c r="C294" s="4">
-        <f>IFERROR(VLOOKUP(B294,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B294,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D294" s="7" t="n"/>
@@ -5701,7 +7277,7 @@
       </c>
       <c r="B295" s="6" t="n"/>
       <c r="C295" s="4">
-        <f>IFERROR(VLOOKUP(B295,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B295,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D295" s="7" t="n"/>
@@ -5716,7 +7292,7 @@
       </c>
       <c r="B296" s="6" t="n"/>
       <c r="C296" s="4">
-        <f>IFERROR(VLOOKUP(B296,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B296,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D296" s="7" t="n"/>
@@ -5731,7 +7307,7 @@
       </c>
       <c r="B297" s="6" t="n"/>
       <c r="C297" s="4">
-        <f>IFERROR(VLOOKUP(B297,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B297,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D297" s="7" t="n"/>
@@ -5746,7 +7322,7 @@
       </c>
       <c r="B298" s="6" t="n"/>
       <c r="C298" s="4">
-        <f>IFERROR(VLOOKUP(B298,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B298,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D298" s="7" t="n"/>
@@ -5761,7 +7337,7 @@
       </c>
       <c r="B299" s="6" t="n"/>
       <c r="C299" s="4">
-        <f>IFERROR(VLOOKUP(B299,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B299,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D299" s="7" t="n"/>
@@ -5776,7 +7352,7 @@
       </c>
       <c r="B300" s="6" t="n"/>
       <c r="C300" s="4">
-        <f>IFERROR(VLOOKUP(B300,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B300,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D300" s="7" t="n"/>
@@ -5791,7 +7367,7 @@
       </c>
       <c r="B301" s="6" t="n"/>
       <c r="C301" s="4">
-        <f>IFERROR(VLOOKUP(B301,Ертегілер!$B$2:$C$15,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B301,Ертегілер!$B$2:$C$8,2,0),"")</f>
         <v/>
       </c>
       <c r="D301" s="7" t="n"/>
@@ -5803,7 +7379,7 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B172 B173 B174 B175 B176 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B201 B202 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B222 B223 B224 B225 B226 B227 B228 B229 B230 B231 B232 B233 B234 B235 B236 B237 B238 B239 B240 B241 B242 B243 B244 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B258 B259 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B276 B277 B278 B279 B280 B281 B282 B283 B284 B285 B286 B287 B288 B289 B290 B291 B292 B293 B294 B295 B296 B297 B298 B299 B300 B301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Ертегілер!$B$2:$B$15</formula1>
+      <formula1>=Ертегілер!$B$2:$B$8</formula1>
     </dataValidation>
     <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201 F202 F203 F204 F205 F206 F207 F208 F209 F210 F211 F212 F213 F214 F215 F216 F217 F218 F219 F220 F221 F222 F223 F224 F225 F226 F227 F228 F229 F230 F231 F232 F233 F234 F235 F236 F237 F238 F239 F240 F241 F242 F243 F244 F245 F246 F247 F248 F249 F250 F251 F252 F253 F254 F255 F256 F257 F258 F259 F260 F261 F262 F263 F264 F265 F266 F267 F268 F269 F270 F271 F272 F273 F274 F275 F276 F277 F278 F279 F280 F281 F282 F283 F284 F285 F286 F287 F288 F289 F290 F291 F292 F293 F294 F295 F296 F297 F298 F299 F300 F301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Тізімдер!$A$2:$A$8</formula1>
@@ -5826,7 +7402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6327,14 +7903,14 @@
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>COUNTIFS(Ертегілер!$C$2:$C$15,A37,Ертегілер!$F$2:$F$15,"иә")</f>
+        <f>COUNTIFS(Ертегілер!$C$2:$C$8,A37,Ертегілер!$F$2:$F$8,"иә")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Хайуанаттар</t>
+          <t>Тұрмыс-салт</t>
         </is>
       </c>
       <c r="B38" s="4">
@@ -6346,45 +7922,7 @@
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>COUNTIFS(Ертегілер!$C$2:$C$15,A38,Ертегілер!$F$2:$F$15,"иә")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Тұрмыс-салт</t>
-        </is>
-      </c>
-      <c r="B39" s="4">
-        <f>COUNTIF(Сандар!$C$2:$C$301,A39)</f>
-        <v/>
-      </c>
-      <c r="C39" s="4">
-        <f>COUNTIFS(Сандар!$C$2:$C$301,A39,Сандар!$G$2:$G$301,"Ф")</f>
-        <v/>
-      </c>
-      <c r="D39" s="4">
-        <f>COUNTIFS(Ертегілер!$C$2:$C$15,A39,Ертегілер!$F$2:$F$15,"иә")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Аңыз-ертегі</t>
-        </is>
-      </c>
-      <c r="B40" s="4">
-        <f>COUNTIF(Сандар!$C$2:$C$301,A40)</f>
-        <v/>
-      </c>
-      <c r="C40" s="4">
-        <f>COUNTIFS(Сандар!$C$2:$C$301,A40,Сандар!$G$2:$G$301,"Ф")</f>
-        <v/>
-      </c>
-      <c r="D40" s="4">
-        <f>COUNTIFS(Ертегілер!$C$2:$C$15,A40,Ертегілер!$F$2:$F$15,"иә")</f>
+        <f>COUNTIFS(Ертегілер!$C$2:$C$8,A38,Ертегілер!$F$2:$F$8,"иә")</f>
         <v/>
       </c>
     </row>
